--- a/data/601633_长城汽车_财务数据.xlsx
+++ b/data/601633_长城汽车_财务数据.xlsx
@@ -11657,7 +11657,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>归属于少数股东的综合收益总额</t>
+          <t>minority_common_profit_total</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
@@ -18999,7 +18999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AA11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -19029,8 +19029,6 @@
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
     <col width="16" customWidth="1" min="27" max="27"/>
-    <col width="16" customWidth="1" min="28" max="28"/>
-    <col width="16" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19077,22 +19075,22 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>财务费用率(%)</t>
+          <t>资产负债率(%)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>资产负债率(%)</t>
+          <t>流动比率</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>流动比率</t>
+          <t>速动比率</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>速动比率</t>
+          <t>产权比率(%)</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -19102,75 +19100,65 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>应收账款周转天数(天)</t>
+          <t>存货周转率(次)</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>存货周转率(次)</t>
+          <t>总资产周转率(次)</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>存货周转天数(天)</t>
+          <t>流动资产周转率(次)</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>总资产周转率(次)</t>
+          <t>固定资产周转率(次)</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>流动资产周转率(次)</t>
+          <t>营收同比(%)</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>固定资产周转率(次)</t>
+          <t>净利润同比(%)</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>营收同比(%)</t>
+          <t>总资产增长率(%)</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>净利润同比(%)</t>
+          <t>经营现金流/净利润</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>总资产增长率(%)</t>
+          <t>自由现金流(元)</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>经营现金流/净利润</t>
+          <t>现金收入比</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>自由现金流(元)</t>
+          <t>现金流组合</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>现金收入比</t>
+          <t>Altman Z-score</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>现金流组合</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Altman Z-score</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Z-score判定</t>
         </is>
@@ -19204,58 +19192,52 @@
         <v>4.647020088431822</v>
       </c>
       <c r="I2" s="4" t="inlineStr"/>
-      <c r="J2" s="6" t="n">
-        <v>-0.003919557846055944</v>
+      <c r="J2" s="3" t="n">
+        <v>48.70164339338526</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>48.70164339338526</v>
+        <v>1.246832516415426</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>1.246832516415426</v>
+        <v>1.10670026819569</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>1.10670026819569</v>
+        <v>94.93601385310639</v>
       </c>
       <c r="N2" s="3" t="n">
         <v>2.442528411969532</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>147.3882548247265</v>
+        <v>14.25005295852995</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>14.25005295852995</v>
+        <v>1.066457930602867</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>25.26306400738725</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>1.066457930602867</v>
-      </c>
-      <c r="S2" s="3" t="n">
         <v>1.82546478853323</v>
       </c>
+      <c r="R2" s="4" t="inlineStr"/>
+      <c r="S2" s="4" t="inlineStr"/>
       <c r="T2" s="4" t="inlineStr"/>
       <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="inlineStr"/>
-      <c r="W2" s="4" t="inlineStr"/>
-      <c r="X2" s="6" t="n">
+      <c r="V2" s="6" t="n">
         <v>0.8371269630783321</v>
       </c>
-      <c r="Y2" s="3" t="n">
+      <c r="W2" s="3" t="n">
         <v>2151000000</v>
       </c>
+      <c r="X2" s="3" t="n">
+        <v>1.012162640252868</v>
+      </c>
+      <c r="Y2" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
+      </c>
       <c r="Z2" s="3" t="n">
-        <v>1.012162640252868</v>
+        <v>2.841138069527462</v>
       </c>
       <c r="AA2" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB2" s="3" t="n">
-        <v>2.841138069527462</v>
-      </c>
-      <c r="AC2" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -19291,64 +19273,58 @@
       <c r="I3" s="3" t="n">
         <v>3.348113347311137</v>
       </c>
-      <c r="J3" s="6" t="n">
-        <v>0.1379230188666398</v>
+      <c r="J3" s="3" t="n">
+        <v>55.44157688584945</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>55.44157688584945</v>
+        <v>1.176831235882543</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>1.176831235882543</v>
+        <v>1.082148740680355</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>1.082148740680355</v>
+        <v>124.4244589711316</v>
       </c>
       <c r="N3" s="3" t="n">
         <v>2.22688704372597</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>161.6606468721724</v>
-      </c>
-      <c r="P3" s="3" t="n">
         <v>16.46225606424888</v>
       </c>
+      <c r="P3" s="6" t="n">
+        <v>0.9907680145393777</v>
+      </c>
       <c r="Q3" s="3" t="n">
-        <v>21.86820558464115</v>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v>0.9907680145393777</v>
-      </c>
+        <v>1.631079413065955</v>
+      </c>
+      <c r="R3" s="4" t="inlineStr"/>
       <c r="S3" s="3" t="n">
-        <v>1.631079413065955</v>
-      </c>
-      <c r="T3" s="4" t="inlineStr"/>
+        <v>2.080329963605473</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>-52.21330177718902</v>
+      </c>
       <c r="U3" s="3" t="n">
-        <v>2.080329963605473</v>
-      </c>
-      <c r="V3" s="3" t="n">
-        <v>-52.21330177718902</v>
+        <v>19.75755343465967</v>
+      </c>
+      <c r="V3" s="6" t="n">
+        <v>-0.2099779600726103</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>19.75755343465967</v>
-      </c>
-      <c r="X3" s="6" t="n">
-        <v>-0.2099779600726103</v>
-      </c>
-      <c r="Y3" s="3" t="n">
         <v>-6881000000</v>
       </c>
+      <c r="X3" s="3" t="n">
+        <v>1.180337247521219</v>
+      </c>
+      <c r="Y3" s="4" t="inlineStr">
+        <is>
+          <t>−/−/+</t>
+        </is>
+      </c>
       <c r="Z3" s="3" t="n">
-        <v>1.180337247521219</v>
+        <v>2.184780489725919</v>
       </c>
       <c r="AA3" s="4" t="inlineStr">
-        <is>
-          <t>−/−/+</t>
-        </is>
-      </c>
-      <c r="AB3" s="3" t="n">
-        <v>2.184780489725919</v>
-      </c>
-      <c r="AC3" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -19384,64 +19360,58 @@
       <c r="I4" s="3" t="n">
         <v>1.782598737122651</v>
       </c>
-      <c r="J4" s="6" t="n">
-        <v>-0.504985589014496</v>
+      <c r="J4" s="3" t="n">
+        <v>52.87298747763865</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>52.87298747763865</v>
+        <v>1.216020890417257</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>1.216020890417257</v>
+        <v>1.134279777119844</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>1.134279777119844</v>
+        <v>112.1904002733018</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>3.670339233080387</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>98.08357678640637</v>
-      </c>
-      <c r="P4" s="3" t="n">
         <v>18.56132578752694</v>
       </c>
+      <c r="P4" s="6" t="n">
+        <v>0.8797047786087512</v>
+      </c>
       <c r="Q4" s="3" t="n">
-        <v>19.39516627858108</v>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v>0.8797047786087512</v>
-      </c>
+        <v>1.44440380160332</v>
+      </c>
+      <c r="R4" s="4" t="inlineStr"/>
       <c r="S4" s="3" t="n">
-        <v>1.44440380160332</v>
-      </c>
-      <c r="T4" s="4" t="inlineStr"/>
+        <v>-2.678590536031923</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>4.049911299292583</v>
+      </c>
       <c r="U4" s="3" t="n">
-        <v>-2.678590536031923</v>
+        <v>1.133454548743973</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>4.049911299292583</v>
+        <v>3.753687990947732</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>1.133454548743973</v>
+        <v>13036000000</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>3.753687990947732</v>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <v>13036000000</v>
+        <v>1.290134781645861</v>
+      </c>
+      <c r="Y4" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>1.290134781645861</v>
+        <v>2.269533230036285</v>
       </c>
       <c r="AA4" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB4" s="3" t="n">
-        <v>2.269533230036285</v>
-      </c>
-      <c r="AC4" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -19477,64 +19447,58 @@
       <c r="I5" s="3" t="n">
         <v>2.855930228792716</v>
       </c>
-      <c r="J5" s="6" t="n">
-        <v>-0.369084402409679</v>
+      <c r="J5" s="3" t="n">
+        <v>51.90015562000424</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>51.90015562000424</v>
+        <v>1.254615384615385</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>1.254615384615385</v>
+        <v>1.140384615384615</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>1.140384615384615</v>
+        <v>107.9008805308921</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>29.10283924097919</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>12.36992710639347</v>
-      </c>
-      <c r="P5" s="3" t="n">
         <v>17.11458266540348</v>
       </c>
+      <c r="P5" s="6" t="n">
+        <v>0.8457960892103017</v>
+      </c>
       <c r="Q5" s="3" t="n">
-        <v>21.03469345634277</v>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v>0.8457960892103017</v>
-      </c>
+        <v>1.412901902123184</v>
+      </c>
+      <c r="R5" s="4" t="inlineStr"/>
       <c r="S5" s="3" t="n">
-        <v>1.412901902123184</v>
-      </c>
-      <c r="T5" s="4" t="inlineStr"/>
+        <v>-2.752335828528208</v>
+      </c>
+      <c r="T5" s="3" t="n">
+        <v>-13.66150083542868</v>
+      </c>
       <c r="U5" s="3" t="n">
-        <v>-2.752335828528208</v>
+        <v>1.159212880143113</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>-13.66150083542868</v>
+        <v>3.083827804457351</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>1.159212880143113</v>
+        <v>7031999999.999999</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>3.083827804457351</v>
-      </c>
-      <c r="Y5" s="3" t="n">
-        <v>7031999999.999999</v>
+        <v>1.183937280730754</v>
+      </c>
+      <c r="Y5" s="4" t="inlineStr">
+        <is>
+          <t>+/−/+</t>
+        </is>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>1.183937280730754</v>
+        <v>2.244351623070272</v>
       </c>
       <c r="AA5" s="4" t="inlineStr">
-        <is>
-          <t>+/−/+</t>
-        </is>
-      </c>
-      <c r="AB5" s="3" t="n">
-        <v>2.244351623070272</v>
-      </c>
-      <c r="AC5" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -19570,64 +19534,58 @@
       <c r="I6" s="3" t="n">
         <v>2.969267864256546</v>
       </c>
-      <c r="J6" s="6" t="n">
-        <v>0.3842526615142893</v>
+      <c r="J6" s="3" t="n">
+        <v>62.76824382673964</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>62.76824382673964</v>
+        <v>1.224638395387231</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>1.224638395387231</v>
+        <v>1.132259813222285</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1.132259813222285</v>
+        <v>168.58498134003</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>28.98235578894656</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>12.4213505148294</v>
-      </c>
-      <c r="P6" s="3" t="n">
         <v>14.3929148994292</v>
       </c>
+      <c r="P6" s="6" t="n">
+        <v>0.7735297630515112</v>
+      </c>
       <c r="Q6" s="3" t="n">
-        <v>25.01230657691703</v>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v>0.7735297630515112</v>
-      </c>
+        <v>1.230577628598996</v>
+      </c>
+      <c r="R6" s="4" t="inlineStr"/>
       <c r="S6" s="3" t="n">
-        <v>1.230577628598996</v>
-      </c>
-      <c r="T6" s="4" t="inlineStr"/>
+        <v>8.62127454099663</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>18.35811882603719</v>
+      </c>
       <c r="U6" s="3" t="n">
-        <v>8.62127454099663</v>
-      </c>
-      <c r="V6" s="3" t="n">
-        <v>18.35811882603719</v>
+        <v>36.17722996392445</v>
+      </c>
+      <c r="V6" s="6" t="n">
+        <v>0.9661556128322182</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>36.17722996392445</v>
-      </c>
-      <c r="X6" s="6" t="n">
-        <v>0.9661556128322182</v>
-      </c>
-      <c r="Y6" s="3" t="n">
         <v>-2881000000</v>
       </c>
+      <c r="X6" s="3" t="n">
+        <v>1.081285328516558</v>
+      </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>+/−/+</t>
+        </is>
+      </c>
       <c r="Z6" s="3" t="n">
-        <v>1.081285328516558</v>
+        <v>1.736607911392074</v>
       </c>
       <c r="AA6" s="4" t="inlineStr">
-        <is>
-          <t>+/−/+</t>
-        </is>
-      </c>
-      <c r="AB6" s="3" t="n">
-        <v>1.736607911392074</v>
-      </c>
-      <c r="AC6" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -19663,64 +19621,58 @@
       <c r="I7" s="3" t="n">
         <v>3.29135758896104</v>
       </c>
-      <c r="J7" s="6" t="n">
-        <v>-0.3286599651163737</v>
+      <c r="J7" s="3" t="n">
+        <v>64.5808629024902</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>64.5808629024902</v>
-      </c>
-      <c r="L7" s="3" t="n">
         <v>1.133571137169577</v>
       </c>
-      <c r="M7" s="6" t="n">
+      <c r="L7" s="6" t="n">
         <v>0.9874786865696624</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>182.3332474890549</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>21.75512967123924</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>16.54782138466993</v>
-      </c>
-      <c r="P7" s="3" t="n">
         <v>12.28830523642564</v>
       </c>
+      <c r="P7" s="6" t="n">
+        <v>0.8281529786604294</v>
+      </c>
       <c r="Q7" s="3" t="n">
-        <v>29.29614727772785</v>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v>0.8281529786604294</v>
-      </c>
+        <v>1.313066811432821</v>
+      </c>
+      <c r="R7" s="4" t="inlineStr"/>
       <c r="S7" s="3" t="n">
-        <v>1.313066811432821</v>
-      </c>
-      <c r="T7" s="4" t="inlineStr"/>
+        <v>32.03738497377798</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>25.40842545638962</v>
+      </c>
       <c r="U7" s="3" t="n">
-        <v>32.03738497377798</v>
+        <v>13.89316347533618</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>25.40842545638962</v>
+        <v>5.251438477305392</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>13.89316347533618</v>
+        <v>22225000000</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>5.251438477305392</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>22225000000</v>
+        <v>1.186733623278766</v>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>1.186733623278766</v>
+        <v>1.731363748301848</v>
       </c>
       <c r="AA7" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB7" s="3" t="n">
-        <v>1.731363748301848</v>
-      </c>
-      <c r="AC7" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -19757,63 +19709,57 @@
         <v>4.6928525628998</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-1.811421586451225</v>
+        <v>64.81600371175624</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>64.81600371175624</v>
-      </c>
-      <c r="L8" s="3" t="n">
         <v>1.123995323688441</v>
       </c>
-      <c r="M8" s="6" t="n">
+      <c r="L8" s="6" t="n">
         <v>0.8904407006116782</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>184.2201300294406</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>15.30165285363044</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>23.52687016517874</v>
-      </c>
-      <c r="P8" s="3" t="n">
         <v>7.186757054239564</v>
       </c>
+      <c r="P8" s="6" t="n">
+        <v>0.7613819810001524</v>
+      </c>
       <c r="Q8" s="3" t="n">
-        <v>50.09213436366701</v>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v>0.7613819810001524</v>
-      </c>
-      <c r="S8" s="3" t="n">
         <v>1.271389884495133</v>
       </c>
-      <c r="T8" s="4" t="inlineStr"/>
-      <c r="U8" s="6" t="n">
+      <c r="R8" s="4" t="inlineStr"/>
+      <c r="S8" s="6" t="n">
         <v>0.6856966090850116</v>
       </c>
+      <c r="T8" s="3" t="n">
+        <v>22.71806384242158</v>
+      </c>
+      <c r="U8" s="3" t="n">
+        <v>5.671919182705463</v>
+      </c>
       <c r="V8" s="3" t="n">
-        <v>22.71806384242158</v>
+        <v>1.491734762573882</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>5.671919182705463</v>
+        <v>-3990000000</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>1.491734762573882</v>
-      </c>
-      <c r="Y8" s="3" t="n">
-        <v>-3990000000</v>
+        <v>1.158104100437716</v>
+      </c>
+      <c r="Y8" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>1.158104100437716</v>
+        <v>1.737530379040417</v>
       </c>
       <c r="AA8" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB8" s="3" t="n">
-        <v>1.737530379040417</v>
-      </c>
-      <c r="AC8" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -19849,64 +19795,58 @@
       <c r="I9" s="3" t="n">
         <v>4.649937117880206</v>
       </c>
-      <c r="J9" s="6" t="n">
-        <v>-0.07268246661340674</v>
+      <c r="J9" s="3" t="n">
+        <v>65.96214040840661</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>65.96214040840661</v>
-      </c>
-      <c r="L9" s="3" t="n">
         <v>1.069914738124239</v>
       </c>
-      <c r="M9" s="6" t="n">
+      <c r="L9" s="6" t="n">
         <v>0.8296657193124916</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>193.7876775314192</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>17.77263254237328</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>20.25586244140775</v>
-      </c>
-      <c r="P9" s="3" t="n">
         <v>6.844816193756708</v>
       </c>
+      <c r="P9" s="6" t="n">
+        <v>0.8960164538843381</v>
+      </c>
       <c r="Q9" s="3" t="n">
-        <v>52.59454597602826</v>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v>0.8960164538843381</v>
-      </c>
+        <v>1.5310549732214</v>
+      </c>
+      <c r="R9" s="4" t="inlineStr"/>
       <c r="S9" s="3" t="n">
-        <v>1.5310549732214</v>
-      </c>
-      <c r="T9" s="4" t="inlineStr"/>
+        <v>26.11918992212546</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>-14.90395685677529</v>
+      </c>
       <c r="U9" s="3" t="n">
-        <v>26.11918992212546</v>
+        <v>8.585054786169392</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>-14.90395685677529</v>
+        <v>2.528046909104279</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>8.585054786169392</v>
+        <v>1041000000</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>2.528046909104279</v>
-      </c>
-      <c r="Y9" s="3" t="n">
-        <v>1041000000</v>
+        <v>1.052161046799609</v>
+      </c>
+      <c r="Y9" s="4" t="inlineStr">
+        <is>
+          <t>+/−/+</t>
+        </is>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>1.052161046799609</v>
+        <v>1.765338396121757</v>
       </c>
       <c r="AA9" s="4" t="inlineStr">
-        <is>
-          <t>+/−/+</t>
-        </is>
-      </c>
-      <c r="AB9" s="3" t="n">
-        <v>1.765338396121757</v>
-      </c>
-      <c r="AC9" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -19942,64 +19882,58 @@
       <c r="I10" s="3" t="n">
         <v>4.601409382029704</v>
       </c>
-      <c r="J10" s="6" t="n">
-        <v>0.04911065535526143</v>
+      <c r="J10" s="3" t="n">
+        <v>63.71807826566233</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>63.71807826566233</v>
-      </c>
-      <c r="L10" s="3" t="n">
         <v>1.089483560414457</v>
       </c>
-      <c r="M10" s="6" t="n">
+      <c r="L10" s="6" t="n">
         <v>0.8819286938076203</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>175.6193586773512</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>20.44116460016074</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>17.61152101858076</v>
-      </c>
-      <c r="P10" s="3" t="n">
         <v>7.382032799628178</v>
       </c>
+      <c r="P10" s="6" t="n">
+        <v>0.9651484743907491</v>
+      </c>
       <c r="Q10" s="3" t="n">
-        <v>48.7670550607866</v>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v>0.9651484743907491</v>
-      </c>
+        <v>1.603936028133126</v>
+      </c>
+      <c r="R10" s="4" t="inlineStr"/>
       <c r="S10" s="3" t="n">
-        <v>1.603936028133126</v>
-      </c>
-      <c r="T10" s="4" t="inlineStr"/>
+        <v>16.73191813583313</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>80.26982938909045</v>
+      </c>
       <c r="U10" s="3" t="n">
-        <v>16.73191813583313</v>
+        <v>8.17310080985739</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>80.26982938909045</v>
+        <v>2.193599727123886</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>8.17310080985739</v>
+        <v>15893000000</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>2.193599727123886</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>15893000000</v>
+        <v>1.105271390619165</v>
+      </c>
+      <c r="Y10" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>1.105271390619165</v>
+        <v>1.999314263670364</v>
       </c>
       <c r="AA10" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB10" s="3" t="n">
-        <v>1.999314263670364</v>
-      </c>
-      <c r="AC10" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -20035,64 +19969,58 @@
       <c r="I11" s="3" t="n">
         <v>4.681871509301352</v>
       </c>
-      <c r="J11" s="6" t="n">
-        <v>-0.8839858315173159</v>
+      <c r="J11" s="3" t="n">
+        <v>60.98682575192642</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>60.98682575192642</v>
-      </c>
-      <c r="L11" s="3" t="n">
         <v>1.090566964568676</v>
       </c>
-      <c r="M11" s="6" t="n">
+      <c r="L11" s="6" t="n">
         <v>0.8833983013247131</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>156.3236699585855</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>21.33105863643978</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>16.87679951266052</v>
+        <v>8.358063097294719</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>8.358063097294719</v>
+        <v>1.005960337132738</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>43.07218021798882</v>
-      </c>
-      <c r="R11" s="3" t="n">
-        <v>1.005960337132738</v>
-      </c>
+        <v>1.643337489287756</v>
+      </c>
+      <c r="R11" s="4" t="inlineStr"/>
       <c r="S11" s="3" t="n">
-        <v>1.643337489287756</v>
-      </c>
-      <c r="T11" s="4" t="inlineStr"/>
+        <v>10.20331036406652</v>
+      </c>
+      <c r="T11" s="3" t="n">
+        <v>-22.07527300732541</v>
+      </c>
       <c r="U11" s="3" t="n">
-        <v>10.20331036406652</v>
+        <v>3.476024251332001</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-22.07527300732541</v>
+        <v>4.09060860128956</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>3.476024251332001</v>
+        <v>28846000000</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>4.09060860128956</v>
-      </c>
-      <c r="Y11" s="3" t="n">
-        <v>28846000000</v>
+        <v>1.103358421135457</v>
+      </c>
+      <c r="Y11" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>1.103358421135457</v>
+        <v>2.080041391824969</v>
       </c>
       <c r="AA11" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB11" s="3" t="n">
-        <v>2.080041391824969</v>
-      </c>
-      <c r="AC11" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>

--- a/data/601633_长城汽车_财务数据.xlsx
+++ b/data/601633_长城汽车_财务数据.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="财务分析指标" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据质量校验" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合并报表" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="财务指标表" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -40354,4 +40355,2123 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>毛利率</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>营业利润率</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>净利润率</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>净资产收益率</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>存货周转率</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>总资产周转率</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>应收账款周转率</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>流动比率</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>速动比率</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>利息保障倍数</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>资产负债率</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>货币资金占比</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>营业收入增长率</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>营业利润增长率</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>净利润增长率</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2016Q1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.138191119910887</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.1402385751832852</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.1150105597737014</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.05442104772331872</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3.729270998166908</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.2562280842498556</v>
+      </c>
+      <c r="H2" t="n">
+        <v>36.03182520624028</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.365531119735518</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.201811125485123</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.4200985893483727</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.03618257497194324</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-0.7882605157249684</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-0.7615805521516436</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-0.7728503253589529</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2016Q2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.1376908326995719</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.139760368949004</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1184650378454448</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.1196071419202797</v>
+      </c>
+      <c r="F3" t="n">
+        <v>8.107776177364673</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.5855078911529746</v>
+      </c>
+      <c r="H3" t="n">
+        <v>60.03018928471861</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.349558771620191</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.119025767737381</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.4190547908909621</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.04943591459928321</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.9957830139787394</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.9889774978908177</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.055728715237069</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2016Q3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.1328662271853293</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.1349979096423461</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1138615467536347</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1686257670857798</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10.05552564532723</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8581487234464306</v>
+      </c>
+      <c r="H4" t="n">
+        <v>86.24190210423417</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.380430114631165</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.150209771728717</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.4210110376438977</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.05171096651826875</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.5226748665045793</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.4707883614564647</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.4635044959787031</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2017年报</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.04691149851440257</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.05825513128079805</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.05018713548389239</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.108075586033773</v>
+      </c>
+      <c r="F5" t="n">
+        <v>17.06653702455453</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.077837261729296</v>
+      </c>
+      <c r="H5" t="n">
+        <v>126.0082986566771</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.176831235882543</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.072298364497886</v>
+      </c>
+      <c r="K5" t="n">
+        <v>31.76641686433234</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.5544157688584945</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.04370086931350466</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.5864256127961813</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-0.3154158269153484</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.3007458669361758</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2017Q1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.09235156944328649</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.09981288453476968</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.08443367282760897</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.03971167679167852</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3.342525104821017</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.2315421443856795</v>
+      </c>
+      <c r="H6" t="n">
+        <v>31.3919763603383</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.363983685270277</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.152640817801642</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.450426884245912</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.02989859412046262</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.7691482040916409</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-0.6044643082412842</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0.6116202923426817</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2017Q2</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.05930457540472811</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.06818472794802581</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.05925296562061435</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.05050416282893638</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5.035157372804075</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.4741684886313793</v>
+      </c>
+      <c r="H7" t="n">
+        <v>32.43102387591772</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.277915275699321</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.014849775526649</v>
+      </c>
+      <c r="K7" t="n">
+        <v>34.15166294359085</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.4392117206592269</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.07932151155091673</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.76703290499499</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.2071052596453364</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.2400495733963375</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2017Q3</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.04272616515213257</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.05273210915759234</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.0459319222916553</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.06161096259582981</v>
+      </c>
+      <c r="F8" t="n">
+        <v>7.942124104574251</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7308587306829178</v>
+      </c>
+      <c r="H8" t="n">
+        <v>46.13107516574881</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.223904933666033</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.030338216765077</v>
+      </c>
+      <c r="K8" t="n">
+        <v>28.07501154925013</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.4734131294017534</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.05679031698223063</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.5366591535658456</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.1884080301033708</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.1911928473296796</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2018年报</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.04915770889904236</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.06372235500000652</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.05365691911190357</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.104687513801554</v>
+      </c>
+      <c r="F9" t="n">
+        <v>16.40508815304048</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9725958222539792</v>
+      </c>
+      <c r="H9" t="n">
+        <v>47.12110778350277</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.216020890417257</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.126170028871439</v>
+      </c>
+      <c r="K9" t="n">
+        <v>14.49982786523985</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.5287298747763864</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.06871198568872987</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.5525762856063101</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.8761589251119943</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.8136941807674405</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2018Q1</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.08623555313273579</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.09710869296322508</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.07956758727778573</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.04012979981313818</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5.00092181288263</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.2370276647960816</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12.38082147903705</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.249464089324659</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.144947527354745</v>
+      </c>
+      <c r="K10" t="n">
+        <v>22.66645414584292</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.5314115090308088</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.0498018518180324</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.7318117784970161</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.5912987261961049</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0.602304976235976</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2018Q2</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.07726324559214781</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.09080800390682291</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.07749591829877661</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.0722280164826016</v>
+      </c>
+      <c r="F11" t="n">
+        <v>8.514178937112073</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.4488163475892339</v>
+      </c>
+      <c r="H11" t="n">
+        <v>107.2881924055929</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.254690585911784</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.138701448321264</v>
+      </c>
+      <c r="K11" t="n">
+        <v>17.76479279308725</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.5077163752231415</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.08376681958654049</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.8284434020604086</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.709808777475609</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.7808369632388057</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2018Q3</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.05171733421064073</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.06966912196973919</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.06042750673541526</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.07664865072948387</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10.79494598721633</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.6213922649007156</v>
+      </c>
+      <c r="H12" t="n">
+        <v>122.3400108167133</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.251613420451357</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.117248566961959</v>
+      </c>
+      <c r="K12" t="n">
+        <v>12.87675513432939</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.5175268363568181</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.09931092673323021</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.3660561104111419</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.04805662143390155</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.06518338804080726</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2019年报</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.03889356904811803</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.05022542380606027</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.04763772894069754</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.08508268014909277</v>
+      </c>
+      <c r="F13" t="n">
+        <v>14.63480403713096</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.8655592087724392</v>
+      </c>
+      <c r="H13" t="n">
+        <v>44.60979298288931</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.254615384615385</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.132307692307692</v>
+      </c>
+      <c r="K13" t="n">
+        <v>28.49873030298259</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.5190015562000424</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.08597121029921483</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.4517419231082085</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.04658062687807529</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.1444736339641826</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2019Q1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.01513333990689769</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.04241009870894485</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.03590709141185899</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.0143459589054311</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4.021302255916066</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.1966857592276112</v>
+      </c>
+      <c r="H14" t="n">
+        <v>6.8556419469657</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.282312589935148</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.185093926790326</v>
+      </c>
+      <c r="K14" t="n">
+        <v>17.05628641851498</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.5192949407965555</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.065410836024399</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-0.7677857564985768</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-0.8039194447308973</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0.8249677670629276</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2019Q2</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.01683181312493698</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.04412598362181593</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.03847086584646746</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.02893069636985975</v>
+      </c>
+      <c r="F15" t="n">
+        <v>7.574683741935793</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.3946565287021936</v>
+      </c>
+      <c r="H15" t="n">
+        <v>14.09436357372138</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.440866979297724</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.252859430401464</v>
+      </c>
+      <c r="K15" t="n">
+        <v>21.67708749166792</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.4454941077622423</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.0839563091108861</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.8254971499875114</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.8993555731817044</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.9558380586928843</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2019Q3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.03444151974130627</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.05495266158474129</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.04798840837172279</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.05585285813801223</v>
+      </c>
+      <c r="F16" t="n">
+        <v>9.487488126425948</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.6416479703066851</v>
+      </c>
+      <c r="H16" t="n">
+        <v>23.60858112628407</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.433983214977405</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.242014202711426</v>
+      </c>
+      <c r="K16" t="n">
+        <v>26.40106484837786</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.4639746715084816</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.09831986324233014</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.5254226551036032</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.8996978210852198</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.9028062847540799</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2020年报</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.04321331466721678</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.05567457637688811</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.05190798953880419</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.09720467298058623</v>
+      </c>
+      <c r="F17" t="n">
+        <v>13.98957512870002</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.817074308026986</v>
+      </c>
+      <c r="H17" t="n">
+        <v>30.95359017519101</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.224638395387231</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.125224847842693</v>
+      </c>
+      <c r="K17" t="n">
+        <v>22.85669221507047</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.6276824382673964</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.09472050697677438</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.6797888267211492</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.7018562637973851</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.8169900566283623</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2020Q1</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>-0.09216246042446219</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.06674838502462917</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.05236281309799705</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.01172920707872162</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.087667366425987</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.09594570082120117</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3.72409755604979</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.323931103475273</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.183267365490844</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-16.56321436032561</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.4893659653642479</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.1031343924431086</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-0.8798138724995637</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-1.144091440565474</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-1.121239211674203</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2020Q2</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.02414699590849068</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.03229914365527219</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.03190004023284239</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.02146475373666814</v>
+      </c>
+      <c r="F19" t="n">
+        <v>7.058911124590296</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.3205559548896363</v>
+      </c>
+      <c r="H19" t="n">
+        <v>10.68049751719679</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.264873148305806</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.178596969180998</v>
+      </c>
+      <c r="K19" t="n">
+        <v>10.49092270800599</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.5536640332431323</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.1560952724043464</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.893748783861386</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-2.400267701424097</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-2.76290571815073</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2020Q3</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.03302380858188914</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.04631080071876197</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.0416329249665985</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.04799313617663427</v>
+      </c>
+      <c r="F20" t="n">
+        <v>11.61407919474101</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.5036528559962881</v>
+      </c>
+      <c r="H20" t="n">
+        <v>15.99986082995108</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.381179443976411</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.270918281381634</v>
+      </c>
+      <c r="K20" t="n">
+        <v>17.76361211322682</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.5719264096446063</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.09040248650006279</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.7296090770255474</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.479928946178649</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.257322699274105</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2021年报</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.03318487169362183</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.04669024744289342</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.04930194003736876</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.1153071021689639</v>
+      </c>
+      <c r="F21" t="n">
+        <v>13.27208693174861</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.900907898120773</v>
+      </c>
+      <c r="H21" t="n">
+        <v>29.67253927314988</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.133571137169576</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.9691831333619256</v>
+      </c>
+      <c r="K21" t="n">
+        <v>14.50591763413653</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.645808629024902</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.1884064580862903</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.194996291101584</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.212980954273296</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.59932674951276</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2021Q1</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.03944325470217858</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.05990469519659739</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.05268724137158302</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.0276307005364456</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.641359228275009</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.1936357578347029</v>
+      </c>
+      <c r="H22" t="n">
+        <v>7.523446767504836</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.26539685185957</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.132816515928257</v>
+      </c>
+      <c r="K22" t="n">
+        <v>20.17764232026016</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.6126694476981143</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.09035612272157491</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-0.7718774773734934</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-0.707313391257262</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-0.7562135201412529</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2021Q2</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.04730380357240593</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.06230975328566181</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.05697900795056544</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.06084976503888669</v>
+      </c>
+      <c r="F23" t="n">
+        <v>6.449026782248456</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.4085429411259801</v>
+      </c>
+      <c r="H23" t="n">
+        <v>20.40473440400988</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.317221214217651</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.179313135532379</v>
+      </c>
+      <c r="K23" t="n">
+        <v>17.66041906810872</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.6218809248113604</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.1416992199926198</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.9901795487358556</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.070081422982427</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.152294433688737</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2021Q3</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.04030775854574864</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.05813252856217371</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.05446128167460736</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.08351449607822936</v>
+      </c>
+      <c r="F24" t="n">
+        <v>7.737982818624456</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.5605910987575248</v>
+      </c>
+      <c r="H24" t="n">
+        <v>24.01408582186194</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.250818621052873</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.08377412928488</v>
+      </c>
+      <c r="K24" t="n">
+        <v>15.5056087787974</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.6462556069946509</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.1272817769675454</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.4661658312908046</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.3678745713154459</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.4013804941793651</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2022年报</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.04917006598237084</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.05800933409165705</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.06009034876672978</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.1331192818774458</v>
+      </c>
+      <c r="F25" t="n">
+        <v>7.405828222880961</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.7800903981833104</v>
+      </c>
+      <c r="H25" t="n">
+        <v>25.07805810056788</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.123995323688441</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.8671739629652826</v>
+      </c>
+      <c r="K25" t="n">
+        <v>12.12268972997069</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.6481600371175623</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.1929951391099338</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.5126005726171237</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.5093950690676357</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.6689415518419017</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2022Q1</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.02631966735119229</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.03988254730779262</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.04853919639221463</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.02513045089884184</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.686864581057947</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.1866199241438591</v>
+      </c>
+      <c r="H26" t="n">
+        <v>6.237925485597922</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.182471859774878</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.9722797782382259</v>
+      </c>
+      <c r="K26" t="n">
+        <v>10.091918695996</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.6293643534926261</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.1469818223390877</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.7552111327326237</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.831702884853212</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-0.8022668340793928</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2022Q2</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.07553942828038318</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.0853481611121661</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.08999696559010389</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.08327326649488137</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3.131383891182708</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.3431989792970217</v>
+      </c>
+      <c r="H27" t="n">
+        <v>12.4955487195274</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.262819590879421</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.011583267875516</v>
+      </c>
+      <c r="K27" t="n">
+        <v>18.51866832050884</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.6275674866950222</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.2300585632761237</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.8481680792935553</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.955056977092552</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.426705248535773</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2022Q3</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.06945476266741479</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.0808781796659945</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.08191612903619656</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.115778072668303</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4.317172356700478</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.535067865027942</v>
+      </c>
+      <c r="H28" t="n">
+        <v>20.59634628030228</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.267675663233009</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.9814467399436037</v>
+      </c>
+      <c r="K28" t="n">
+        <v>17.52713453408774</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.613869427268888</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.186156561664158</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.60105846715984</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.5172054403437736</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.4572992670408671</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2023年报</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.03177499450185861</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.04157312059315554</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.04054459051237522</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.1004579648166191</v>
+      </c>
+      <c r="F29" t="n">
+        <v>6.808828873018959</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.8975556101500139</v>
+      </c>
+      <c r="H29" t="n">
+        <v>31.27700916539726</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.069914738124239</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.7947218838814454</v>
+      </c>
+      <c r="K29" t="n">
+        <v>8.606770935188266</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.6596214040840662</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.1904754806975704</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.7411687066450035</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-0.1050019064064539</v>
+      </c>
+      <c r="P29" t="n">
+        <v>-0.1382042455559686</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2023Q1</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>-0.01172056384962805</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.002433189995241147</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.006048609447496481</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.002643402863038119</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.161151452446298</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.1530889562688471</v>
+      </c>
+      <c r="H30" t="n">
+        <v>4.478834823922265</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.088985481664534</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.7981554212082432</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.652269380146713</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.6443699536210401</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.1473233837550113</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-0.8323527659016775</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-1.009812050837604</v>
+      </c>
+      <c r="P30" t="n">
+        <v>-0.974989693293258</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2023Q2</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.01117884473089537</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.01751250232305588</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.01947471975786674</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.02166258695809231</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.911195207892201</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.3862382647584877</v>
+      </c>
+      <c r="H31" t="n">
+        <v>11.58366313430676</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.068980066479372</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.7825424757906003</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.736287306057946</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.6615026353929748</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.1510614852651406</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1.409596071530687</v>
+      </c>
+      <c r="O31" t="n">
+        <v>-18.34268876776527</v>
+      </c>
+      <c r="P31" t="n">
+        <v>6.758181220005781</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2023Q3</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.03610613377416183</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.0448112734809254</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.04181641564562463</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.07797947470364618</v>
+      </c>
+      <c r="F32" t="n">
+        <v>4.752402813732156</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.6363731036942092</v>
+      </c>
+      <c r="H32" t="n">
+        <v>19.9222389902609</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.101086945712382</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.8171584275584992</v>
+      </c>
+      <c r="K32" t="n">
+        <v>8.711676468664809</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.656390773122067</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.1177817030216248</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.7078982790151589</v>
+      </c>
+      <c r="O32" t="n">
+        <v>3.370197670597386</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.667225264532793</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2024年报</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.04950665522287145</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.0685646117181376</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.06261326405869097</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.1749373317976992</v>
+      </c>
+      <c r="F33" t="n">
+        <v>7.632703519024584</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.9885437825062947</v>
+      </c>
+      <c r="H33" t="n">
+        <v>31.19552258620535</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.089483560414457</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.8660683690952109</v>
+      </c>
+      <c r="K33" t="n">
+        <v>16.54848788160474</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.6371807826566231</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.1413237185375712</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.6919478848615712</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.58880725231427</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.533416077221001</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2024Q1</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0.05418241263768431</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.08452672568884065</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.07509487059284244</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.04270042673834032</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.573679968891089</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.2073343775245808</v>
+      </c>
+      <c r="H34" t="n">
+        <v>6.315396279608045</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.138012760255205</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.8483169663393267</v>
+      </c>
+      <c r="K34" t="n">
+        <v>16.28168821079317</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.6331413856003434</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.1764982397694583</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-0.78802791595596</v>
+      </c>
+      <c r="O34" t="n">
+        <v>-0.7386799727629358</v>
+      </c>
+      <c r="P34" t="n">
+        <v>-0.7457724579625582</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2024Q2</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.06255071126382894</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.08866295395824532</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.07720198230696813</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.09686684882354153</v>
+      </c>
+      <c r="F35" t="n">
+        <v>3.244088629674111</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.4637044984155644</v>
+      </c>
+      <c r="H35" t="n">
+        <v>13.97015639752464</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.100998763435746</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.8232378959383621</v>
+      </c>
+      <c r="K35" t="n">
+        <v>18.89837964977104</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.6277671770137396</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.1990554970975164</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1.133198549954168</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.237584424062839</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.193054670854026</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2024Q3</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.06096474512778871</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.08309222174345222</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.07311179097586118</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.1375046352303695</v>
+      </c>
+      <c r="F36" t="n">
+        <v>5.149177351620538</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.7059774402643215</v>
+      </c>
+      <c r="H36" t="n">
+        <v>20.41215903012484</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.130033705871918</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.872048402005546</v>
+      </c>
+      <c r="K36" t="n">
+        <v>18.13920073579722</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.6215705750815919</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.2082780825068136</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.5558999527052766</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.4581420774870406</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.4734677623850749</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2025年报</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.03247563655020536</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.05176126924741574</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.04427381983150164</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.1194177589095949</v>
+      </c>
+      <c r="F37" t="n">
+        <v>8.409739600617113</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.037214342146912</v>
+      </c>
+      <c r="H37" t="n">
+        <v>26.60905642658825</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.090566964568676</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.8666650820815111</v>
+      </c>
+      <c r="K37" t="n">
+        <v>16.68056848758101</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.6098682575192642</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.1280405525371968</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.5664012580867932</v>
+      </c>
+      <c r="O37" t="n">
+        <v>-0.02422975859698473</v>
+      </c>
+      <c r="P37" t="n">
+        <v>-0.05144483319702597</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2025Q1</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.0354650644486606</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.0430692763568392</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.04375859463422156</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.0205351819992495</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.313879234855421</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.1828043914513001</v>
+      </c>
+      <c r="H38" t="n">
+        <v>4.579104109564621</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.106008951361936</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.8025542851148642</v>
+      </c>
+      <c r="K38" t="n">
+        <v>10.35300895146902</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.61108837104264</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.147534427679525</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-0.820400686065302</v>
+      </c>
+      <c r="O38" t="n">
+        <v>-0.8505598375422677</v>
+      </c>
+      <c r="P38" t="n">
+        <v>-0.8224907269134949</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2025Q2</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.04145507858181474</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.07431338707502759</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.06863014336093566</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.0758406232137728</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.687279492300101</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.4248454390808284</v>
+      </c>
+      <c r="H39" t="n">
+        <v>11.21586798584998</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.095483954242566</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.8141386598686652</v>
+      </c>
+      <c r="K39" t="n">
+        <v>19.58660607878215</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.6198075875512657</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.1260945315067507</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1.307265243231785</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2.981044252623347</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.618670703168903</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2025Q3</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0.04137656280387936</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.06364525461764763</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.0562238413859362</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.1010670077807299</v>
+      </c>
+      <c r="F40" t="n">
+        <v>4.6873457212735</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.6932592244675359</v>
+      </c>
+      <c r="H40" t="n">
+        <v>17.47930069443351</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.107153988746534</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.8469463081743467</v>
+      </c>
+      <c r="K40" t="n">
+        <v>18.6022190528427</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.6088347778858992</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.1050080336735387</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.6633181964320074</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.424538892504009</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.3626394157259658</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/601633_长城汽车_财务数据.xlsx
+++ b/data/601633_长城汽车_财务数据.xlsx
@@ -40363,7 +40363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:S40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40442,6 +40442,21 @@
           <t>净利润增长率</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>有息负债率</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>经营现金流/营收</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>权益乘数</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -40494,6 +40509,15 @@
       <c r="P2" t="n">
         <v>-0.7728503253589529</v>
       </c>
+      <c r="Q2" t="n">
+        <v>0.006262771866520819</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-0.007963765488083949</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.726884674827662</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -40546,6 +40570,15 @@
       <c r="P3" t="n">
         <v>1.055728715237069</v>
       </c>
+      <c r="Q3" t="n">
+        <v>0.006187849502851804</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.1051899784061111</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.723774038461539</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -40598,6 +40631,15 @@
       <c r="P4" t="n">
         <v>0.4635044959787031</v>
       </c>
+      <c r="Q4" t="n">
+        <v>0.00392945127894418</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.1040971444222926</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.729509317053169</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -40650,6 +40692,15 @@
       <c r="P5" t="n">
         <v>-0.3007458669361758</v>
       </c>
+      <c r="Q5" t="n">
+        <v>0.1230698255040842</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-0.01053819233079544</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.249862623384553</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -40702,6 +40753,15 @@
       <c r="P6" t="n">
         <v>-0.6116202923426817</v>
       </c>
+      <c r="Q6" t="n">
+        <v>0.07506038603248104</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-0.2315649939071248</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.821918919467034</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -40754,6 +40814,15 @@
       <c r="P7" t="n">
         <v>0.2400495733963375</v>
       </c>
+      <c r="Q7" t="n">
+        <v>0.07731951316407237</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.2034258971231937</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.785811028700419</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -40806,6 +40875,15 @@
       <c r="P8" t="n">
         <v>0.1911928473296796</v>
       </c>
+      <c r="Q8" t="n">
+        <v>0.07600942773006684</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.1127286306314549</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.901933642829763</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -40858,6 +40936,15 @@
       <c r="P9" t="n">
         <v>0.8136941807674405</v>
       </c>
+      <c r="Q9" t="n">
+        <v>0.1337924865831843</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.2014113329016063</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.128510233222275</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -40910,6 +40997,15 @@
       <c r="P10" t="n">
         <v>-0.602304976235976</v>
       </c>
+      <c r="Q10" t="n">
+        <v>0.1833372902094709</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-0.03728729897319892</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.139446745330937</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -40962,6 +41058,15 @@
       <c r="P11" t="n">
         <v>0.7808369632388057</v>
       </c>
+      <c r="Q11" t="n">
+        <v>0.1820738238286274</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.3117531066850306</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.037068173375824</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -41014,6 +41119,15 @@
       <c r="P12" t="n">
         <v>0.06518338804080726</v>
       </c>
+      <c r="Q12" t="n">
+        <v>0.1860865541649088</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.2512322891413065</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.078956087863254</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -41066,6 +41180,15 @@
       <c r="P13" t="n">
         <v>0.1444736339641826</v>
       </c>
+      <c r="Q13" t="n">
+        <v>0.04921482634222254</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.1469065530485257</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.079008805308921</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -41118,6 +41241,15 @@
       <c r="P14" t="n">
         <v>-0.8249677670629276</v>
       </c>
+      <c r="Q14" t="n">
+        <v>0.1835217079296735</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-0.07860378476195848</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.087405909448377</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -41170,6 +41302,15 @@
       <c r="P15" t="n">
         <v>0.9558380586928843</v>
       </c>
+      <c r="Q15" t="n">
+        <v>0.04999789516771872</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.151623659204017</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.803407346970492</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -41222,6 +41363,15 @@
       <c r="P16" t="n">
         <v>0.9028062847540799</v>
       </c>
+      <c r="Q16" t="n">
+        <v>0.05222468516401817</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.1610722440189991</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.865583484299517</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -41274,6 +41424,15 @@
       <c r="P17" t="n">
         <v>0.8169900566283623</v>
       </c>
+      <c r="Q17" t="n">
+        <v>0.1270688457317984</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.05015119544375173</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.685832374175997</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -41326,6 +41485,15 @@
       <c r="P18" t="n">
         <v>-1.121239211674203</v>
       </c>
+      <c r="Q18" t="n">
+        <v>0.06704832784695387</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.04228366844013872</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.958349683278211</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -41378,6 +41546,15 @@
       <c r="P19" t="n">
         <v>-2.76290571815073</v>
       </c>
+      <c r="Q19" t="n">
+        <v>0.09907592805140622</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.2648820926313635</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.240464749605826</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -41430,6 +41607,15 @@
       <c r="P20" t="n">
         <v>1.257322699274105</v>
       </c>
+      <c r="Q20" t="n">
+        <v>0.1290813763656913</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-0.004183867493771982</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.336046938027136</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -41482,6 +41668,15 @@
       <c r="P21" t="n">
         <v>1.59932674951276</v>
       </c>
+      <c r="Q21" t="n">
+        <v>0.1197436832983672</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.2589061049180416</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.823514261798983</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -41534,6 +41729,15 @@
       <c r="P22" t="n">
         <v>-0.7562135201412529</v>
       </c>
+      <c r="Q22" t="n">
+        <v>0.1384693367308496</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.006845138202405511</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.581774130796166</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -41586,6 +41790,15 @@
       <c r="P23" t="n">
         <v>1.152294433688737</v>
       </c>
+      <c r="Q23" t="n">
+        <v>0.1354260774408632</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.2439915706556685</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.644669538295867</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -41638,6 +41851,15 @@
       <c r="P24" t="n">
         <v>0.4013804941793651</v>
       </c>
+      <c r="Q24" t="n">
+        <v>0.1279114394684449</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.1836729464842256</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.826899930495516</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -41690,6 +41912,15 @@
       <c r="P25" t="n">
         <v>0.6689415518419017</v>
       </c>
+      <c r="Q25" t="n">
+        <v>0.1604687171242521</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.08963886215051944</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.842855170932961</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -41742,6 +41973,15 @@
       <c r="P26" t="n">
         <v>-0.8022668340793928</v>
       </c>
+      <c r="Q26" t="n">
+        <v>0.1371384474677032</v>
+      </c>
+      <c r="R26" t="n">
+        <v>-0.3412325718607953</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.698317214998534</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -41794,6 +42034,15 @@
       <c r="P27" t="n">
         <v>2.426705248535773</v>
       </c>
+      <c r="Q27" t="n">
+        <v>0.1528041977472375</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.13139319466569</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.685975084677651</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -41846,6 +42095,15 @@
       <c r="P28" t="n">
         <v>0.4572992670408671</v>
       </c>
+      <c r="Q28" t="n">
+        <v>0.1606982360011695</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.04610960740653516</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.59074203955674</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -41898,6 +42156,15 @@
       <c r="P29" t="n">
         <v>-0.1382042455559686</v>
       </c>
+      <c r="Q29" t="n">
+        <v>0.1457743329855418</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.1024986267257089</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.93820528167472</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -41950,6 +42217,15 @@
       <c r="P30" t="n">
         <v>-0.974989693293258</v>
       </c>
+      <c r="Q30" t="n">
+        <v>0.1597996608608744</v>
+      </c>
+      <c r="R30" t="n">
+        <v>-0.2825212312224336</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.812488156149327</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -42002,6 +42278,15 @@
       <c r="P31" t="n">
         <v>6.758181220005781</v>
       </c>
+      <c r="Q31" t="n">
+        <v>0.1672158199573343</v>
+      </c>
+      <c r="R31" t="n">
+        <v>-0.03481436482331585</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.954327501323027</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -42054,6 +42339,15 @@
       <c r="P32" t="n">
         <v>2.667225264532793</v>
       </c>
+      <c r="Q32" t="n">
+        <v>0.1613188122537287</v>
+      </c>
+      <c r="R32" t="n">
+        <v>-0.01565643858170777</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.910326996197719</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -42106,6 +42400,15 @@
       <c r="P33" t="n">
         <v>1.533416077221001</v>
       </c>
+      <c r="Q33" t="n">
+        <v>0.09450211280543817</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.1373484389534804</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.756472747990125</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -42158,6 +42461,15 @@
       <c r="P34" t="n">
         <v>-0.7457724579625582</v>
       </c>
+      <c r="Q34" t="n">
+        <v>0.1509761742960355</v>
+      </c>
+      <c r="R34" t="n">
+        <v>-0.06145671043515187</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.726149517348971</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -42210,6 +42522,15 @@
       <c r="P35" t="n">
         <v>1.193054670854026</v>
       </c>
+      <c r="Q35" t="n">
+        <v>0.1416150194086284</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.1023431757824418</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.686781375970565</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -42262,6 +42583,15 @@
       <c r="P36" t="n">
         <v>0.4734677623850749</v>
       </c>
+      <c r="Q36" t="n">
+        <v>0.1285456351439294</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.09963281005107121</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.642808188178091</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -42314,6 +42644,15 @@
       <c r="P37" t="n">
         <v>-0.05144483319702597</v>
       </c>
+      <c r="Q37" t="n">
+        <v>0.06429991832676396</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.1811068682146849</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.563236699585855</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -42366,6 +42705,15 @@
       <c r="P38" t="n">
         <v>-0.8224907269134949</v>
       </c>
+      <c r="Q38" t="n">
+        <v>0.09762076152568608</v>
+      </c>
+      <c r="R38" t="n">
+        <v>-0.2243929625062694</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.571278217318719</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -42418,6 +42766,15 @@
       <c r="P39" t="n">
         <v>2.618670703168903</v>
       </c>
+      <c r="Q39" t="n">
+        <v>0.09235257307756374</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.09980003906754788</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.630278271166371</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -42469,6 +42826,15 @@
       </c>
       <c r="P40" t="n">
         <v>0.3626394157259658</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.0765484622869945</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.1392482018023619</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.556464489852591</v>
       </c>
     </row>
   </sheetData>
